--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92556017895</v>
+        <v>46157.93114628993</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114628993</v>
+        <v>46157.93138215502</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93138215502</v>
+        <v>46157.93385168113</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93385168113</v>
+        <v>46157.93696656539</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696656539</v>
+        <v>46158.28205526645</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205526645</v>
+        <v>46158.29653650954</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29653650954</v>
+        <v>46158.29808821352</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808821352</v>
+        <v>46158.33371485903</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33371485903</v>
+        <v>46158.37222943529</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Апрель 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37222943529</v>
+        <v>46158.37276188735</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
